--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -247,12 +253,6 @@
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t>Report
@@ -1063,16 +1063,16 @@
     <t>Need to be able to provide a conclusion that is not lost among the basic result data.</t>
   </si>
   <si>
+    <t>1446: source value from MICROBIOLOGY - VIROLOGY RPT REMARK &gt; VIROLOGY RPT REMARK - VIROLOGY RPT REMARK (#63.05-37 &gt; 63.44-.01)</t>
+  </si>
+  <si>
+    <t>Micro.VirologyReports.VirologyReportRemark</t>
+  </si>
+  <si>
     <t>OBX</t>
   </si>
   <si>
     <t>inboundRelationship[typeCode="SPRT"].source[classCode=OBS, moodCode=EVN, code=LOINC:48767-8].value (type=ST)</t>
-  </si>
-  <si>
-    <t>1446: source value from MICROBIOLOGY - VIROLOGY RPT REMARK &gt; VIROLOGY RPT REMARK - VIROLOGY RPT REMARK (#63.05-37 &gt; 63.44-.01)</t>
-  </si>
-  <si>
-    <t>Micro.VirologyReports.VirologyReportRemark</t>
   </si>
   <si>
     <t>DiagnosticReport.conclusionCode</t>
@@ -1467,12 +1467,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="133.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="133.91796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="121.93359375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1705,19 +1705,19 @@
         <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2309,13 +2309,13 @@
         <v>82</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO7" t="s" s="2">
         <v>126</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP7" t="s" s="2">
         <v>82</v>
@@ -2429,13 +2429,13 @@
         <v>82</v>
       </c>
       <c r="AM8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO8" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP8" t="s" s="2">
         <v>82</v>
@@ -2549,13 +2549,13 @@
         <v>82</v>
       </c>
       <c r="AM9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN9" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO9" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO9" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP9" t="s" s="2">
         <v>82</v>
@@ -2671,13 +2671,13 @@
         <v>82</v>
       </c>
       <c r="AM10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN10" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO10" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO10" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP10" t="s" s="2">
         <v>82</v>
@@ -2787,22 +2787,22 @@
         <v>103</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -2909,19 +2909,19 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AN12" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AM12" t="s" s="2">
+      <c r="AO12" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -3027,22 +3027,22 @@
         <v>103</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AO13" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="AN13" t="s" s="2">
+      <c r="AP13" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="14" hidden="true">
@@ -3148,19 +3148,19 @@
         <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AM14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="15" hidden="true">
@@ -3270,19 +3270,19 @@
         <v>82</v>
       </c>
       <c r="AL15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN15" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="AM15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="AN15" t="s" s="2">
+      <c r="AP15" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="16" hidden="true">
@@ -3387,22 +3387,22 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AN16" t="s" s="2">
+      <c r="AP16" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
@@ -3507,22 +3507,22 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -3629,22 +3629,22 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -3751,22 +3751,22 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP19" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -3876,19 +3876,19 @@
         <v>82</v>
       </c>
       <c r="AL20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -3995,22 +3995,22 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4117,22 +4117,22 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>82</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4242,16 +4242,16 @@
         <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN23" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4364,16 +4364,16 @@
         <v>82</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4487,13 +4487,13 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4604,16 +4604,16 @@
         <v>82</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -4725,13 +4725,13 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -4845,13 +4845,13 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -4967,13 +4967,13 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5089,13 +5089,13 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO30" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
@@ -5207,13 +5207,13 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5321,22 +5321,22 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>331</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -5442,16 +5442,16 @@
         <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -5564,16 +5564,16 @@
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$47</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="437">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -513,6 +513,209 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>DiagnosticReport.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>1605: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - IEN (#63.05-.35 &gt; 63.5-.001)</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
     <t>DiagnosticReport.basedOn</t>
   </si>
   <si>
@@ -536,6 +739,9 @@
     <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
+    <t>1690: reference from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (#63.05-.35 &gt; 63.5-3)</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
@@ -557,16 +763,16 @@
     <t>Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-report-status</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFDiagnosticReportLabStatus</t>
   </si>
   <si>
     <t>us-core-8
 us-core-9</t>
   </si>
   <si>
+    <t>1416: terminologyMaps using VF_DiagnosticReportLabStatus on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (#63.05-.35 &gt; 63.5-10)</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -586,10 +792,6 @@
 Sub-departmentServiceDiscipline</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Service category</t>
   </si>
   <si>
@@ -597,37 +799,6 @@
   </si>
   <si>
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>OBR-24</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:LaboratorySlice</t>
-  </si>
-  <si>
-    <t>LaboratorySlice</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -638,6 +809,98 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes for diagnostic service sections.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074#LAB</t>
+  </si>
+  <si>
+    <t>OBR-24</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (#60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:LaboratorySlice</t>
+  </si>
+  <si>
+    <t>LaboratorySlice</t>
+  </si>
+  <si>
     <t>DiagnosticReport.code</t>
   </si>
   <si>
@@ -654,9 +917,6 @@
     <t>UsageNote= The typical patterns for codes are:  1)  a LOINC code either as a  translation from a "local" code or as a primary code, or 2)  a local code only if no suitable LOINC exists,  or 3)  both the local and the LOINC translation.   Systems SHALL be capable of sending the local code if one exists.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
     <t>LOINC codes</t>
   </si>
   <si>
@@ -695,6 +955,12 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
+    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -765,6 +1031,10 @@
     <t>Need to know where in the patient history to file/present this report.</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">us-core-8
 </t>
   </si>
@@ -781,6 +1051,22 @@
     <t>FiveWs.done[x]</t>
   </si>
   <si>
+    <t>DiagnosticReport.effective[x]:effectiveDateTime</t>
+  </si>
+  <si>
+    <t>effectiveDateTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>1424: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (#63.05-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime</t>
+  </si>
+  <si>
     <t>DiagnosticReport.issued</t>
   </si>
   <si>
@@ -808,6 +1094,12 @@
 </t>
   </si>
   <si>
+    <t>1429: source value from MICROBIOLOGY - DATE REPORT COMPLETED (#63.05-.03)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.ReportCompletedDateTime</t>
+  </si>
+  <si>
     <t>OBR-22</t>
   </si>
   <si>
@@ -840,6 +1132,9 @@
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
   </si>
   <si>
+    <t>1682: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (#63.05-.112)</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -904,7 +1199,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LaboratoryResultsObservation)
 </t>
   </si>
   <si>
@@ -918,6 +1213,9 @@
   </si>
   <si>
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
+  </si>
+  <si>
+    <t>1437: reference from See mapping for Laboratory Results</t>
   </si>
   <si>
     <t>OBXs</t>
@@ -971,29 +1269,7 @@
     <t>DiagnosticReport.media.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DiagnosticReport.media.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>DiagnosticReport.media.modifierExtension</t>
@@ -1429,12 +1705,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP34"/>
+  <dimension ref="A1:AP47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="40.49609375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.37890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.34765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1451,24 +1727,24 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="48.453125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="65.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="133.91796875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="165.01953125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="121.93359375" customWidth="true" bestFit="true"/>
@@ -2814,14 +3090,14 @@
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>82</v>
@@ -2833,20 +3109,16 @@
         <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M12" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>165</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -2894,19 +3166,19 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>82</v>
@@ -2915,13 +3187,13 @@
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -2929,44 +3201,44 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
       </c>
@@ -2990,41 +3262,43 @@
         <v>82</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>82</v>
@@ -3033,58 +3307,60 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="AP13" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G14" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="G14" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>92</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>182</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3108,35 +3384,37 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AC14" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>82</v>
@@ -3154,37 +3432,35 @@
         <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>191</v>
+        <v>134</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>193</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>181</v>
+        <v>82</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>82</v>
@@ -3204,7 +3480,9 @@
       <c r="N15" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="O15" s="2"/>
+      <c r="O15" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3213,7 +3491,7 @@
         <v>82</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>82</v>
@@ -3228,13 +3506,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3252,13 +3530,13 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
@@ -3279,32 +3557,32 @@
         <v>191</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="AP15" t="s" s="2">
-        <v>193</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
@@ -3313,18 +3591,20 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>182</v>
+        <v>105</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
@@ -3336,7 +3616,7 @@
         <v>82</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>82</v>
@@ -3348,13 +3628,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>202</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>203</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>204</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3372,10 +3652,10 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>91</v>
@@ -3393,32 +3673,32 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>91</v>
@@ -3433,18 +3713,18 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
@@ -3456,7 +3736,7 @@
         <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -3492,7 +3772,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3507,34 +3787,34 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>218</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>220</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3553,20 +3833,16 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
       </c>
@@ -3614,7 +3890,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3635,28 +3911,28 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>231</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3666,7 +3942,7 @@
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>82</v>
@@ -3675,20 +3951,18 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -3736,7 +4010,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3745,7 +4019,7 @@
         <v>91</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>103</v>
@@ -3757,35 +4031,35 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>238</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>241</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>92</v>
@@ -3794,22 +4068,22 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -3858,80 +4132,78 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>92</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>255</v>
+        <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -3956,13 +4228,11 @@
         <v>82</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -3980,59 +4250,59 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>82</v>
+        <v>241</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>82</v>
+        <v>242</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>263</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>82</v>
@@ -4041,20 +4311,18 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>266</v>
+        <v>182</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4063,7 +4331,7 @@
         <v>82</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>82</v>
@@ -4078,31 +4346,29 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4117,30 +4383,30 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AP22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>263</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4151,7 +4417,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -4163,20 +4429,16 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>160</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>161</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
@@ -4224,19 +4486,19 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>271</v>
+        <v>163</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -4248,10 +4510,10 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>217</v>
+        <v>164</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4259,14 +4521,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>279</v>
+        <v>136</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4276,7 +4538,7 @@
         <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
@@ -4285,20 +4547,18 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>280</v>
+        <v>137</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>281</v>
+        <v>138</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>282</v>
+        <v>166</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -4334,19 +4594,19 @@
         <v>82</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>278</v>
+        <v>170</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4358,7 +4618,7 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -4370,10 +4630,10 @@
         <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>286</v>
+        <v>164</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4381,10 +4641,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>287</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4404,21 +4664,23 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4466,7 +4728,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4490,10 +4752,10 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4501,24 +4763,24 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>82</v>
@@ -4527,17 +4789,19 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>295</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4586,13 +4850,13 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -4601,7 +4865,7 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
@@ -4610,10 +4874,10 @@
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -4621,41 +4885,45 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C27" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>302</v>
+        <v>249</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>251</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -4665,7 +4933,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -4680,13 +4948,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -4704,19 +4972,19 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>304</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -4728,53 +4996,53 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>82</v>
+        <v>258</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>306</v>
+        <v>283</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>136</v>
+        <v>284</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>138</v>
+        <v>285</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>140</v>
+        <v>287</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4800,13 +5068,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -4824,19 +5092,19 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -4845,59 +5113,57 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>137</v>
+        <v>296</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>140</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>146</v>
+        <v>299</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -4946,49 +5212,49 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>82</v>
+        <v>300</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>134</v>
+        <v>304</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5004,22 +5270,22 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5068,7 +5334,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5089,38 +5355,38 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>82</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5129,16 +5395,20 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5174,28 +5444,26 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
@@ -5207,28 +5475,30 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>82</v>
+        <v>327</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="C32" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="D32" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5244,20 +5514,22 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5306,7 +5578,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5315,68 +5587,72 @@
         <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>182</v>
+        <v>337</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5400,13 +5676,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>337</v>
+        <v>82</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5424,49 +5700,49 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5476,28 +5752,28 @@
         <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5546,7 +5822,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5561,26 +5837,1592 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>332</v>
+        <v>357</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="AP34" t="s" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AP36" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="P37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AP40" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP42" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AP43" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AP44" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP34">
+  <autoFilter ref="A1:AP47">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5590,7 +7432,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI33">
+  <conditionalFormatting sqref="A2:AI46">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (#63.05) to us-core-diagnosticreport-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-diagnosticreport-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -660,7 +660,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1605: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - IEN (#63.05-.35 &gt; 63.5-.001)</t>
+    <t>1605: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - IEN (63.05-.35 &gt; 63.5-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -739,7 +739,7 @@
     <t>This allows tracing of authorization for the report and tracking whether proposals/recommendations were acted upon.</t>
   </si>
   <si>
-    <t>1690: reference from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (#63.05-.35 &gt; 63.5-3)</t>
+    <t>1690: reference from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.05-.35 &gt; 63.5-3)</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -770,7 +770,7 @@
 us-core-9</t>
   </si>
   <si>
-    <t>1416: terminologyMaps using VF_DiagnosticReportLabStatus on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (#63.05-.35 &gt; 63.5-10)</t>
+    <t>1416: terminologyMaps using VF_DiagnosticReportLabStatus on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (63.05-.35 &gt; 63.5-10)</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -886,7 +886,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (#60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -955,7 +955,7 @@
     <t>SHALL know the subject context.</t>
   </si>
   <si>
-    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+    <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
@@ -1061,7 +1061,7 @@
 </t>
   </si>
   <si>
-    <t>1424: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (#63.05-.01)</t>
+    <t>1424: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime</t>
@@ -1094,7 +1094,7 @@
 </t>
   </si>
   <si>
-    <t>1429: source value from MICROBIOLOGY - DATE REPORT COMPLETED (#63.05-.03)</t>
+    <t>1429: source value from MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
@@ -1132,7 +1132,7 @@
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
   </si>
   <si>
-    <t>1682: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (#63.05-.112)</t>
+    <t>1682: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1339,7 +1339,7 @@
     <t>Need to be able to provide a conclusion that is not lost among the basic result data.</t>
   </si>
   <si>
-    <t>1446: source value from MICROBIOLOGY - VIROLOGY RPT REMARK &gt; VIROLOGY RPT REMARK - VIROLOGY RPT REMARK (#63.05-37 &gt; 63.44-.01)</t>
+    <t>1446: source value from MICROBIOLOGY - VIROLOGY RPT REMARK &gt; VIROLOGY RPT REMARK - VIROLOGY RPT REMARK (63.05-37 &gt; 63.44-.01)</t>
   </si>
   <si>
     <t>Micro.VirologyReports.VirologyReportRemark</t>
@@ -1743,7 +1743,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="165.01953125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="163.48046875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="171.66796875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$51</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="444">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -799,6 +799,95 @@
   </si>
   <si>
     <t>Multiple categories are allowed using various categorization schemes.   The level of granularity is defined by the category concepts in the value set. More fine-grained filtering can be performed using the metadata and/or terminology hierarchy in DiagnosticReport.code.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes for diagnostic service sections.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>OBR-24</t>
+  </si>
+  <si>
+    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:LaboratorySlice</t>
+  </si>
+  <si>
+    <t>LaboratorySlice</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -809,96 +898,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
     <t>1419: fixed value = http://terminology.hl7.org/CodeSystem/v2-0074#LAB</t>
-  </si>
-  <si>
-    <t>OBR-24</t>
-  </si>
-  <si>
-    <t>inboundRelationship[typeCode=COMP].source[classCode=LIST, moodCode=EVN, code &lt; LabService].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:LaboratorySlice</t>
-  </si>
-  <si>
-    <t>LaboratorySlice</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -933,6 +933,27 @@
   </si>
   <si>
     <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding</t>
+  </si>
+  <si>
+    <t>1420: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.text</t>
+  </si>
+  <si>
+    <t>1661: source value from LABORATORY TEST - NAME (60-.01)</t>
+  </si>
+  <si>
+    <t>Dim.LabChemTest.LabChemTestName</t>
   </si>
   <si>
     <t>DiagnosticReport.subject</t>
@@ -1705,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP47"/>
+  <dimension ref="A1:AP51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
@@ -4331,34 +4352,34 @@
         <v>82</v>
       </c>
       <c r="S22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X22" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="T22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X22" t="s" s="2">
+      <c r="Y22" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="Y22" t="s" s="2">
+      <c r="Z22" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="Z22" t="s" s="2">
+      <c r="AA22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB22" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -4383,30 +4404,30 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>260</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4521,10 +4542,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4641,10 +4662,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4667,19 +4688,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4728,7 +4749,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4752,10 +4773,10 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4763,10 +4784,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4792,16 +4813,16 @@
         <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4850,7 +4871,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4865,19 +4886,19 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -4885,13 +4906,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>247</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>248</v>
@@ -4933,28 +4954,28 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X27" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="T27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X27" t="s" s="2">
+      <c r="Y27" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -4987,7 +5008,7 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -4996,13 +5017,13 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AP27" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>260</v>
       </c>
     </row>
     <row r="28" hidden="true">
@@ -5134,37 +5155,35 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>296</v>
+        <v>160</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>297</v>
+        <v>161</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>298</v>
+        <v>162</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>299</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5212,7 +5231,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>163</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5224,44 +5243,44 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>300</v>
+        <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>301</v>
+        <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>304</v>
+        <v>164</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>305</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>307</v>
+        <v>136</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5270,23 +5289,21 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>308</v>
+        <v>137</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>309</v>
+        <v>138</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>166</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5322,31 +5339,31 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>170</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -5355,35 +5372,35 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>315</v>
+        <v>164</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>92</v>
@@ -5395,19 +5412,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>320</v>
+        <v>263</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>321</v>
+        <v>264</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>322</v>
+        <v>265</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>323</v>
+        <v>266</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5444,61 +5461,61 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>317</v>
+        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>328</v>
+        <v>269</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>318</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5517,19 +5534,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>332</v>
+        <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>271</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>272</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>322</v>
+        <v>273</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>323</v>
+        <v>274</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5578,7 +5595,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5587,44 +5604,44 @@
         <v>91</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>333</v>
+        <v>299</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>334</v>
+        <v>300</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>328</v>
+        <v>278</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>301</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>301</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>336</v>
+        <v>302</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>91</v>
@@ -5639,19 +5656,17 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>337</v>
+        <v>303</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>341</v>
+        <v>306</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5700,7 +5715,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>335</v>
+        <v>301</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5709,50 +5724,50 @@
         <v>91</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>342</v>
+        <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>343</v>
+        <v>307</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>344</v>
+        <v>308</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>309</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>347</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>349</v>
+        <v>314</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -5761,19 +5776,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>352</v>
+        <v>317</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>353</v>
+        <v>318</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>354</v>
+        <v>319</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5822,13 +5837,13 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
@@ -5837,44 +5852,44 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>356</v>
+        <v>320</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>358</v>
+        <v>322</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>359</v>
+        <v>323</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>361</v>
+        <v>325</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -5883,19 +5898,19 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>362</v>
+        <v>326</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>363</v>
+        <v>327</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>364</v>
+        <v>328</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>365</v>
+        <v>329</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -5932,28 +5947,26 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>360</v>
+        <v>324</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>103</v>
@@ -5965,59 +5978,61 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>356</v>
+        <v>333</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>358</v>
+        <v>335</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>359</v>
+        <v>336</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>369</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>370</v>
+        <v>328</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>371</v>
+        <v>329</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>372</v>
+        <v>330</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6066,56 +6081,56 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>367</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>332</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>333</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>373</v>
+        <v>334</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>336</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>374</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>374</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>92</v>
@@ -6124,22 +6139,22 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>380</v>
+        <v>348</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6188,49 +6203,49 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>374</v>
+        <v>342</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>381</v>
+        <v>350</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6240,27 +6255,29 @@
         <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6308,7 +6325,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6323,34 +6340,34 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6369,17 +6386,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6428,7 +6447,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6449,24 +6468,24 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>396</v>
+        <v>373</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>397</v>
+        <v>374</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>397</v>
+        <v>374</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6477,7 +6496,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6489,16 +6508,20 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>160</v>
+        <v>375</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>161</v>
+        <v>376</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -6546,19 +6569,19 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6570,10 +6593,10 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>164</v>
+        <v>311</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6581,14 +6604,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>136</v>
+        <v>382</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6598,7 +6621,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
@@ -6607,18 +6630,20 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>138</v>
+        <v>384</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>166</v>
+        <v>385</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>386</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6666,7 +6691,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>170</v>
+        <v>381</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6678,10 +6703,10 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
@@ -6690,10 +6715,10 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>164</v>
+        <v>390</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6701,14 +6726,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6721,26 +6746,24 @@
         <v>82</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>137</v>
+        <v>392</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>146</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -6788,7 +6811,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6800,7 +6823,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -6815,7 +6838,7 @@
         <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>134</v>
+        <v>396</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -6823,21 +6846,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -6846,22 +6869,20 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>160</v>
+        <v>399</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>407</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -6910,13 +6931,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -6934,10 +6955,10 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -6945,10 +6966,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6956,7 +6977,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>91</v>
@@ -6968,16 +6989,16 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>411</v>
+        <v>160</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>412</v>
+        <v>161</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>413</v>
+        <v>162</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7028,10 +7049,10 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>410</v>
+        <v>163</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>91</v>
@@ -7040,7 +7061,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7055,7 +7076,7 @@
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>414</v>
+        <v>164</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7063,24 +7084,24 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>416</v>
+        <v>136</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
@@ -7089,18 +7110,18 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>417</v>
+        <v>138</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7148,34 +7169,34 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>415</v>
+        <v>170</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>423</v>
+        <v>164</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7183,14 +7204,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7203,22 +7224,26 @@
         <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>182</v>
+        <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7242,13 +7267,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7266,7 +7291,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7278,7 +7303,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7290,10 +7315,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>422</v>
+        <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>429</v>
+        <v>134</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7301,10 +7326,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7315,7 +7340,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7327,19 +7352,19 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>431</v>
+        <v>160</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7388,13 +7413,13 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
@@ -7412,17 +7437,495 @@
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AO47" t="s" s="2">
+      <c r="B49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AP47" t="s" s="2">
+      <c r="AP50" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AP51" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP47">
+  <autoFilter ref="A1:AP51">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7432,7 +7935,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI46">
+  <conditionalFormatting sqref="A2:AI50">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -875,7 +875,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WLKD CODE - WKLD CODE LAB SECTION &gt; WLKD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+    <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="448">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -742,6 +742,9 @@
     <t>1690: reference from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - CPRS ORDER # (63.05-.35 &gt; 63.5-3)</t>
   </si>
   <si>
+    <t>Micro.MicroOrderedTest.CPRSOrderIEN,SStaff.SMicroOrderedTest.CPRSOrderIEN</t>
+  </si>
+  <si>
     <t>Event.basedOn</t>
   </si>
   <si>
@@ -773,6 +776,9 @@
     <t>1416: terminologyMaps using VF_DiagnosticReportLabStatus on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (63.05-.35 &gt; 63.5-10)</t>
   </si>
   <si>
+    <t>Micro.MicroOrderedTest.DispositionLabCodeIEN,SStaff.SMicroOrderedTest.DispositionLabCodeIEN</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -876,6 +882,9 @@
   </si>
   <si>
     <t>1662: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - WKLD CODE LAB SECTION &gt; WKLD CODE LAB SECT - NAME (60-64 &gt; 64-13 &gt; 64.21-.01)</t>
+  </si>
+  <si>
+    <t>Dim.LabChemTest.NationalVALabCodeIEN</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -979,7 +988,7 @@
     <t>1421: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Pathology.Autopsy.LRDFN,Micro.BacteriologyReports.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,SStaff.SMicroOrderedTest.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN</t>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1085,7 +1094,7 @@
     <t>1424: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
-    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime</t>
+    <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime</t>
   </si>
   <si>
     <t>DiagnosticReport.issued</t>
@@ -1154,6 +1163,9 @@
   </si>
   <si>
     <t>1682: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -4171,16 +4183,16 @@
         <v>232</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4188,10 +4200,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4217,14 +4229,14 @@
         <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4253,7 +4265,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4271,7 +4283,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>91</v>
@@ -4280,40 +4292,40 @@
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4335,13 +4347,13 @@
         <v>182</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4367,19 +4379,19 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -4389,7 +4401,7 @@
         <v>169</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4413,21 +4425,21 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4542,10 +4554,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4662,10 +4674,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4688,19 +4700,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4749,7 +4761,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4773,10 +4785,10 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4784,10 +4796,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4813,16 +4825,16 @@
         <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4871,7 +4883,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4886,19 +4898,19 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -4906,16 +4918,16 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4937,13 +4949,13 @@
         <v>182</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4954,7 +4966,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -4969,13 +4981,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -4993,7 +5005,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5008,7 +5020,7 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -5017,25 +5029,25 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5057,13 +5069,13 @@
         <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5092,10 +5104,10 @@
         <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5113,7 +5125,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -5134,24 +5146,24 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5266,10 +5278,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5386,10 +5398,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5412,19 +5424,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5473,7 +5485,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5488,19 +5500,19 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5508,10 +5520,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5537,16 +5549,16 @@
         <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5595,7 +5607,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5610,19 +5622,19 @@
         <v>103</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5630,14 +5642,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5656,17 +5668,17 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5715,7 +5727,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5730,34 +5742,34 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5776,19 +5788,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5837,7 +5849,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5858,28 +5870,28 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5898,19 +5910,19 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -5947,7 +5959,7 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
@@ -5957,7 +5969,7 @@
         <v>169</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5966,7 +5978,7 @@
         <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>103</v>
@@ -5978,30 +5990,30 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6020,19 +6032,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6081,7 +6093,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6090,40 +6102,40 @@
         <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6142,19 +6154,19 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6203,7 +6215,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6212,40 +6224,40 @@
         <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6264,19 +6276,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6325,7 +6337,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6340,34 +6352,34 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6386,19 +6398,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6447,7 +6459,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6468,24 +6480,24 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6508,19 +6520,19 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6569,7 +6581,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6593,10 +6605,10 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6604,14 +6616,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6630,19 +6642,19 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6691,7 +6703,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6706,7 +6718,7 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
@@ -6715,10 +6727,10 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -6726,10 +6738,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6752,16 +6764,16 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6811,7 +6823,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6838,7 +6850,7 @@
         <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -6846,14 +6858,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6872,17 +6884,17 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -6931,7 +6943,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6955,10 +6967,10 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -6966,10 +6978,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7084,10 +7096,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7204,14 +7216,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7233,10 +7245,10 @@
         <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>140</v>
@@ -7291,7 +7303,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7326,10 +7338,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7355,16 +7367,16 @@
         <v>160</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7413,7 +7425,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7440,7 +7452,7 @@
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
@@ -7448,10 +7460,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7474,13 +7486,13 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7531,7 +7543,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -7558,7 +7570,7 @@
         <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7566,14 +7578,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7595,14 +7607,14 @@
         <v>160</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7651,7 +7663,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7666,19 +7678,19 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7686,10 +7698,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7715,10 +7727,10 @@
         <v>182</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7745,31 +7757,31 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="Z50" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7793,10 +7805,10 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -7804,10 +7816,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7830,19 +7842,19 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -7891,7 +7903,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7915,10 +7927,10 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$60</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2337" uniqueCount="502">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -630,10 +630,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>1605-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -956,6 +962,139 @@
     <t>1420: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC (60-64 &gt; 64-25 &gt; 95.3)</t>
   </si>
   <si>
+    <t>DiagnosticReport.code.coding.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1420-2: fixed value = http://loinc.org</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>1420-1: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - CODE (60-64 &gt; 64-25 &gt; 95.3-.01)</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>1420-3: source value from LABORATORY TEST - NATIONAL VA LAB CODE &gt; WKLD CODE - DEFAULT LOINC CODE &gt; LAB LOINC - COMPONENT (60-64 &gt; 64-25 &gt; 95.3-1)</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
     <t>DiagnosticReport.code.text</t>
   </si>
   <si>
@@ -1162,22 +1301,48 @@
     <t>Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
   </si>
   <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>PRT-8 (where this PRT-4-Participation = "PO")</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.performer:va-by</t>
+  </si>
+  <si>
+    <t>va-by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner)
+</t>
+  </si>
+  <si>
+    <t>1434: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.VerifyingStaffIEN</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.performer:va-at</t>
+  </si>
+  <si>
+    <t>va-at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization)
+</t>
+  </si>
+  <si>
     <t>1682: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
   </si>
   <si>
     <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>PRT-8 (where this PRT-4-Participation = "PO")</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>DiagnosticReport.resultsInterpreter</t>
@@ -1738,11 +1903,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP51"/>
+  <dimension ref="A1:AP60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.51953125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.37890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.1328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -3615,7 +3780,7 @@
         <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
@@ -3646,10 +3811,10 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>82</v>
+        <v>197</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>82</v>
@@ -3685,7 +3850,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3700,7 +3865,7 @@
         <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>82</v>
@@ -3709,10 +3874,10 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>82</v>
@@ -3720,10 +3885,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3749,13 +3914,13 @@
         <v>160</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3769,7 +3934,7 @@
         <v>82</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>82</v>
@@ -3805,7 +3970,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3820,7 +3985,7 @@
         <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>82</v>
@@ -3829,10 +3994,10 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>82</v>
@@ -3840,10 +4005,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3866,13 +4031,13 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3923,7 +4088,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3947,10 +4112,10 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>82</v>
@@ -3958,10 +4123,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3984,16 +4149,16 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4043,7 +4208,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4067,10 +4232,10 @@
         <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>82</v>
@@ -4078,14 +4243,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4104,19 +4269,19 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4165,7 +4330,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4180,19 +4345,19 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>82</v>
@@ -4200,10 +4365,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4229,14 +4394,14 @@
         <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4265,7 +4430,7 @@
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>82</v>
@@ -4283,7 +4448,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>91</v>
@@ -4292,40 +4457,40 @@
         <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4347,13 +4512,13 @@
         <v>182</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4379,19 +4544,19 @@
         <v>82</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
@@ -4401,7 +4566,7 @@
         <v>169</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4425,21 +4590,21 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4554,10 +4719,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4674,10 +4839,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4700,19 +4865,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4761,7 +4926,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4785,10 +4950,10 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4796,10 +4961,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4825,16 +4990,16 @@
         <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4883,7 +5048,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4898,19 +5063,19 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -4918,16 +5083,16 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4949,13 +5114,13 @@
         <v>182</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4966,7 +5131,7 @@
         <v>82</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>82</v>
@@ -4981,13 +5146,13 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5005,7 +5170,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5020,7 +5185,7 @@
         <v>103</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>82</v>
@@ -5029,25 +5194,25 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5069,13 +5234,13 @@
         <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5104,10 +5269,10 @@
         <v>187</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5125,7 +5290,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>91</v>
@@ -5146,24 +5311,24 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5278,10 +5443,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5398,10 +5563,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5424,19 +5589,19 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5485,7 +5650,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5500,19 +5665,19 @@
         <v>103</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5520,10 +5685,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5537,29 +5702,25 @@
         <v>91</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
         <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>273</v>
+        <v>161</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5607,7 +5768,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>277</v>
+        <v>163</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5619,22 +5780,22 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>280</v>
+        <v>82</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -5649,37 +5810,37 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>305</v>
+        <v>136</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>306</v>
+        <v>137</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>307</v>
+        <v>138</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>309</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -5715,61 +5876,61 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>167</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>170</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>310</v>
+        <v>82</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>314</v>
+        <v>164</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>315</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5779,7 +5940,7 @@
         <v>91</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -5788,19 +5949,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>318</v>
+        <v>105</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -5810,7 +5971,7 @@
         <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>82</v>
@@ -5849,7 +6010,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5864,34 +6025,34 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>323</v>
+        <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>326</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5901,7 +6062,7 @@
         <v>91</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -5910,20 +6071,18 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>329</v>
+        <v>160</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -5959,17 +6118,19 @@
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="AC35" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5978,7 +6139,7 @@
         <v>91</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>103</v>
@@ -5990,30 +6151,28 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>339</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>328</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6032,19 +6191,17 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>342</v>
+        <v>111</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6093,7 +6250,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6102,40 +6259,40 @@
         <v>91</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>344</v>
+        <v>281</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>336</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>339</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6154,19 +6311,17 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>347</v>
+        <v>160</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6215,7 +6370,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6224,50 +6379,50 @@
         <v>91</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>354</v>
+        <v>281</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
@@ -6276,19 +6431,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>363</v>
+        <v>342</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6337,13 +6492,13 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
@@ -6352,44 +6507,44 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>366</v>
+        <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -6398,19 +6553,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>373</v>
+        <v>160</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>374</v>
+        <v>275</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>375</v>
+        <v>276</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>376</v>
+        <v>277</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>364</v>
+        <v>278</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6459,13 +6614,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>371</v>
+        <v>279</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -6474,65 +6629,63 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>367</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>377</v>
+        <v>282</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>369</v>
+        <v>283</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>378</v>
+        <v>350</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>378</v>
+        <v>350</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>379</v>
+        <v>352</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>380</v>
+        <v>353</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>383</v>
+        <v>355</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6581,13 +6734,13 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>378</v>
+        <v>350</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
@@ -6596,65 +6749,65 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>384</v>
+        <v>359</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>314</v>
+        <v>360</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="I41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K41" t="s" s="2">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>388</v>
+        <v>365</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>389</v>
+        <v>366</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>390</v>
+        <v>367</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -6703,13 +6856,13 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
@@ -6718,64 +6871,66 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>369</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>82</v>
+        <v>372</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -6811,28 +6966,26 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>395</v>
+        <v>373</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>82</v>
+        <v>381</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>103</v>
@@ -6844,38 +6997,40 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="D43" t="s" s="2">
-        <v>402</v>
+        <v>374</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>82</v>
@@ -6884,17 +7039,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>406</v>
+        <v>379</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -6943,49 +7100,49 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>82</v>
+        <v>381</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>82</v>
+        <v>392</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6995,25 +7152,29 @@
         <v>91</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>160</v>
+        <v>393</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>161</v>
+        <v>394</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7061,7 +7222,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>163</v>
+        <v>391</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7070,40 +7231,40 @@
         <v>91</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>164</v>
+        <v>402</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>136</v>
+        <v>405</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7113,27 +7274,29 @@
         <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>137</v>
+        <v>406</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>138</v>
+        <v>407</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>166</v>
+        <v>408</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7169,19 +7332,17 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>170</v>
+        <v>404</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7193,7 +7354,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7202,59 +7363,61 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>164</v>
+        <v>413</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>416</v>
+      </c>
       <c r="D46" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>137</v>
+        <v>417</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>140</v>
+        <v>409</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7303,7 +7466,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7315,37 +7478,39 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>82</v>
+        <v>419</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>134</v>
+        <v>413</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7355,28 +7520,28 @@
         <v>91</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>160</v>
+        <v>422</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -7425,13 +7590,13 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
@@ -7440,41 +7605,41 @@
         <v>103</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7486,16 +7651,20 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>410</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7543,13 +7712,13 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
@@ -7564,38 +7733,38 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>82</v>
@@ -7604,17 +7773,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>160</v>
+        <v>433</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7663,13 +7834,13 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
@@ -7678,19 +7849,19 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>431</v>
+        <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>434</v>
+        <v>360</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -7698,14 +7869,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7715,7 +7886,7 @@
         <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>82</v>
@@ -7724,16 +7895,20 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>182</v>
+        <v>441</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -7757,31 +7932,31 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="Z50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7796,7 +7971,7 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
@@ -7805,10 +7980,10 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -7816,10 +7991,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7842,20 +8017,18 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -7903,7 +8076,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7927,17 +8100,1097 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="AP51" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AP56" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AP57" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP51">
+  <autoFilter ref="A1:AP60">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7947,7 +9200,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI50">
+  <conditionalFormatting sqref="A2:AI59">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -630,7 +630,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/63.5</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -639,7 +639,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1605-1: fixed value = http://va.gov/fhir/identifiers/Sta3n&lt;stationNr&gt;/&lt;fileNr&gt;</t>
+    <t>1605-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/63.5</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -630,7 +630,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/identifiers/Sta3n$stationNr/63.5</t>
+    <t>http://va.gov/identifiers/$Sta3n/63.5</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -639,7 +639,7 @@
     <t>Identifier.system</t>
   </si>
   <si>
-    <t>1605-1: fixed value = http://va.gov/fhir/identifiers/Sta3n$stationNr/63.5</t>
+    <t>1605-1: fixed value = http://va.gov/identifiers/$Sta3n/63.5</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
+++ b/docs/StructureDefinition-LaboratoryResultsMicrobiologyVirologyDiagnosticReport.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
